--- a/HW5/result/HW_5.xlsx
+++ b/HW5/result/HW_5.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\GitHub\DADS7102\HW5\result\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\T00229\Documents\GitHub\DADS7102\HW5\result\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76C35115-8587-4841-9C59-1D3112C74608}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72095350-9FC6-484B-A152-247881C55592}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{33498688-4029-4D37-9392-6E2D196B3B0C}"/>
+    <workbookView xWindow="5850" yWindow="4080" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{33498688-4029-4D37-9392-6E2D196B3B0C}"/>
   </bookViews>
   <sheets>
-    <sheet name="Location" sheetId="1" r:id="rId1"/>
+    <sheet name="WH Location " sheetId="1" r:id="rId1"/>
+    <sheet name="Uncapacitated Facility" sheetId="2" r:id="rId2"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId2"/>
+    <externalReference r:id="rId3"/>
   </externalReferences>
   <definedNames>
     <definedName name="AFinish">[1]project!$K$6</definedName>
@@ -34,16 +35,16 @@
     <definedName name="LFinish">[1]project!$K$17</definedName>
     <definedName name="MFinish">[1]project!$K$18</definedName>
     <definedName name="NFinish">[1]project!$K$19</definedName>
-    <definedName name="solver_adj" localSheetId="0" hidden="1">Location!$B$6:$C$6,Location!$I$2:$J$5</definedName>
+    <definedName name="solver_adj" localSheetId="0" hidden="1">'WH Location '!$B$6:$C$6,'WH Location '!$I$2:$J$5</definedName>
     <definedName name="solver_cvg" localSheetId="0" hidden="1">0.0001</definedName>
     <definedName name="solver_drv" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_eng" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_est" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_itr" localSheetId="0" hidden="1">2147483647</definedName>
-    <definedName name="solver_lhs1" localSheetId="0" hidden="1">Location!$I$2:$I$5</definedName>
-    <definedName name="solver_lhs2" localSheetId="0" hidden="1">Location!$I$2:$I$5</definedName>
-    <definedName name="solver_lhs3" localSheetId="0" hidden="1">Location!$J$2:$J$5</definedName>
-    <definedName name="solver_lhs4" localSheetId="0" hidden="1">Location!$J$2:$J$5</definedName>
+    <definedName name="solver_lhs1" localSheetId="0" hidden="1">'WH Location '!$I$2:$I$5</definedName>
+    <definedName name="solver_lhs2" localSheetId="0" hidden="1">'WH Location '!$I$2:$I$5</definedName>
+    <definedName name="solver_lhs3" localSheetId="0" hidden="1">'WH Location '!$J$2:$J$5</definedName>
+    <definedName name="solver_lhs4" localSheetId="0" hidden="1">'WH Location '!$J$2:$J$5</definedName>
     <definedName name="solver_mip" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_mni" localSheetId="0" hidden="1">30</definedName>
     <definedName name="solver_mrt" localSheetId="0" hidden="1">0.075</definedName>
@@ -52,17 +53,17 @@
     <definedName name="solver_nod" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_num" localSheetId="0" hidden="1">4</definedName>
     <definedName name="solver_nwt" localSheetId="0" hidden="1">1</definedName>
-    <definedName name="solver_opt" localSheetId="0" hidden="1">Location!$F$7</definedName>
+    <definedName name="solver_opt" localSheetId="0" hidden="1">'WH Location '!$F$7</definedName>
     <definedName name="solver_pre" localSheetId="0" hidden="1">0.000001</definedName>
     <definedName name="solver_rbv" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_rel1" localSheetId="0" hidden="1">3</definedName>
     <definedName name="solver_rel2" localSheetId="0" hidden="1">3</definedName>
     <definedName name="solver_rel3" localSheetId="0" hidden="1">3</definedName>
     <definedName name="solver_rel4" localSheetId="0" hidden="1">3</definedName>
-    <definedName name="solver_rhs1" localSheetId="0" hidden="1">Location!$E$2:$E$5</definedName>
-    <definedName name="solver_rhs2" localSheetId="0" hidden="1">Location!$F$2:$F$5</definedName>
-    <definedName name="solver_rhs3" localSheetId="0" hidden="1">Location!$G$2:$G$5</definedName>
-    <definedName name="solver_rhs4" localSheetId="0" hidden="1">Location!$H$2:$H$5</definedName>
+    <definedName name="solver_rhs1" localSheetId="0" hidden="1">'WH Location '!$E$2:$E$5</definedName>
+    <definedName name="solver_rhs2" localSheetId="0" hidden="1">'WH Location '!$F$2:$F$5</definedName>
+    <definedName name="solver_rhs3" localSheetId="0" hidden="1">'WH Location '!$G$2:$G$5</definedName>
+    <definedName name="solver_rhs4" localSheetId="0" hidden="1">'WH Location '!$H$2:$H$5</definedName>
     <definedName name="solver_rlx" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_rsd" localSheetId="0" hidden="1">0</definedName>
     <definedName name="solver_scl" localSheetId="0" hidden="1">1</definedName>
@@ -86,9 +87,10 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -141,13 +143,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="188" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Tahoma"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -250,6 +252,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -259,11 +266,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="188" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -282,12 +284,8 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Sensitivity Report 1"/>
       <sheetName val="ProductMix"/>
@@ -462,9 +460,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -502,9 +500,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -537,9 +535,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -572,9 +587,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -749,19 +781,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1ED6F4FE-D4FD-4FAF-995E-613C0C8290EC}">
   <dimension ref="A1:K7"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.6875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.0625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="9.125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="4.125" customWidth="1"/>
-    <col min="8" max="8" width="5.9375" customWidth="1"/>
-    <col min="9" max="9" width="8.0625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="4.140625" customWidth="1"/>
+    <col min="8" max="8" width="6" customWidth="1"/>
+    <col min="9" max="9" width="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -796,39 +828,39 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A2" s="6">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="3">
         <v>5</v>
       </c>
-      <c r="C2" s="6">
+      <c r="C2" s="3">
         <v>10</v>
       </c>
-      <c r="D2" s="6">
+      <c r="D2" s="3">
         <v>200</v>
       </c>
-      <c r="E2" s="9">
+      <c r="E2" s="6">
         <f>B2-$B$6</f>
         <v>-5</v>
       </c>
-      <c r="F2" s="9">
+      <c r="F2" s="6">
         <f>-E2</f>
         <v>5</v>
       </c>
-      <c r="G2" s="9">
+      <c r="G2" s="6">
         <f>C2 - $C$6</f>
         <v>5</v>
       </c>
-      <c r="H2" s="9">
+      <c r="H2" s="6">
         <f>-G2</f>
         <v>-5</v>
       </c>
-      <c r="I2" s="8">
+      <c r="I2" s="5">
         <v>5</v>
       </c>
-      <c r="J2" s="8">
+      <c r="J2" s="5">
         <v>5</v>
       </c>
       <c r="K2">
@@ -836,39 +868,39 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A3" s="6">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="3">
         <v>2</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="3">
         <v>10</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="3">
         <v>5</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="3">
         <v>150</v>
       </c>
-      <c r="E3" s="9">
+      <c r="E3" s="6">
         <f>B3-$B$6</f>
         <v>0</v>
       </c>
-      <c r="F3" s="9">
+      <c r="F3" s="6">
         <f t="shared" ref="F3:F5" si="0">-E3</f>
         <v>0</v>
       </c>
-      <c r="G3" s="9">
+      <c r="G3" s="6">
         <f>C3 - $C$6</f>
         <v>0</v>
       </c>
-      <c r="H3" s="9">
+      <c r="H3" s="6">
         <f t="shared" ref="H3:H5" si="1">-G3</f>
         <v>0</v>
       </c>
-      <c r="I3" s="8">
+      <c r="I3" s="5">
         <v>0</v>
       </c>
-      <c r="J3" s="8">
+      <c r="J3" s="5">
         <v>0</v>
       </c>
       <c r="K3">
@@ -876,39 +908,39 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A4" s="6">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
         <v>3</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="3">
         <v>0</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="3">
         <v>12</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="3">
         <v>200</v>
       </c>
-      <c r="E4" s="9">
+      <c r="E4" s="6">
         <f>B4-$B$6</f>
         <v>-10</v>
       </c>
-      <c r="F4" s="9">
+      <c r="F4" s="6">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="G4" s="9">
+      <c r="G4" s="6">
         <f>C4 - $C$6</f>
         <v>7</v>
       </c>
-      <c r="H4" s="9">
+      <c r="H4" s="6">
         <f t="shared" si="1"/>
         <v>-7</v>
       </c>
-      <c r="I4" s="8">
+      <c r="I4" s="5">
         <v>10</v>
       </c>
-      <c r="J4" s="8">
+      <c r="J4" s="5">
         <v>7</v>
       </c>
       <c r="K4">
@@ -916,39 +948,39 @@
         <v>3400</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A5" s="6">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
         <v>4</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="3">
         <v>12</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="3">
         <v>0</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="3">
         <v>300</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="6">
         <f>B5-$B$6</f>
         <v>2</v>
       </c>
-      <c r="F5" s="9">
+      <c r="F5" s="6">
         <f t="shared" si="0"/>
         <v>-2</v>
       </c>
-      <c r="G5" s="9">
+      <c r="G5" s="6">
         <f>C5 - $C$6</f>
         <v>-5</v>
       </c>
-      <c r="H5" s="9">
+      <c r="H5" s="6">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="I5" s="8">
+      <c r="I5" s="5">
         <v>2</v>
       </c>
-      <c r="J5" s="8">
+      <c r="J5" s="5">
         <v>5</v>
       </c>
       <c r="K5">
@@ -956,26 +988,26 @@
         <v>2100</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="7">
         <v>10</v>
       </c>
-      <c r="C6" s="10">
+      <c r="C6" s="7">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A7" s="3" t="s">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="7">
+      <c r="B7" s="9"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="4">
         <f>SUM(K2:K5)</f>
         <v>7500</v>
       </c>
@@ -987,4 +1019,13 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D85756CD-BB6F-471C-AEDD-324919B9EA08}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/HW5/result/HW_5.xlsx
+++ b/HW5/result/HW_5.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\T00229\Documents\GitHub\DADS7102\HW5\result\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\GitHub\DADS7102\HW5\result\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72095350-9FC6-484B-A152-247881C55592}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D602E2B7-194A-4E58-A816-AEC7E170A912}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5850" yWindow="4080" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{33498688-4029-4D37-9392-6E2D196B3B0C}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{33498688-4029-4D37-9392-6E2D196B3B0C}"/>
   </bookViews>
   <sheets>
     <sheet name="WH Location " sheetId="1" r:id="rId1"/>
@@ -89,9 +89,6 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -143,13 +140,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="187" formatCode="0.0"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -244,7 +241,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -252,11 +249,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="187" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -284,9 +280,16 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
     <sheetNames>
+      <sheetName val="Advertising "/>
+      <sheetName val="Advertising _Sensitivity Report"/>
+      <sheetName val="monopolist"/>
       <sheetName val="Sensitivity Report 1"/>
       <sheetName val="ProductMix"/>
       <sheetName val="ProductMix_add_on"/>
@@ -324,15 +327,18 @@
       <sheetName val="Location"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8">
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="10" refreshError="1"/>
+      <sheetData sheetId="11">
         <row r="6">
           <cell r="K6">
             <v>2</v>
@@ -404,18 +410,18 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
-      <sheetData sheetId="17"/>
-      <sheetData sheetId="18"/>
-      <sheetData sheetId="19"/>
-      <sheetData sheetId="20">
+      <sheetData sheetId="12" refreshError="1"/>
+      <sheetData sheetId="13" refreshError="1"/>
+      <sheetData sheetId="14" refreshError="1"/>
+      <sheetData sheetId="15" refreshError="1"/>
+      <sheetData sheetId="16" refreshError="1"/>
+      <sheetData sheetId="17" refreshError="1"/>
+      <sheetData sheetId="18" refreshError="1"/>
+      <sheetData sheetId="19" refreshError="1"/>
+      <sheetData sheetId="20" refreshError="1"/>
+      <sheetData sheetId="21" refreshError="1"/>
+      <sheetData sheetId="22" refreshError="1"/>
+      <sheetData sheetId="23">
         <row r="10">
           <cell r="B10">
             <v>0</v>
@@ -440,29 +446,29 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="21"/>
-      <sheetData sheetId="22"/>
-      <sheetData sheetId="23"/>
-      <sheetData sheetId="24"/>
-      <sheetData sheetId="25"/>
-      <sheetData sheetId="26"/>
-      <sheetData sheetId="27"/>
-      <sheetData sheetId="28"/>
-      <sheetData sheetId="29"/>
-      <sheetData sheetId="30"/>
-      <sheetData sheetId="31"/>
-      <sheetData sheetId="32"/>
-      <sheetData sheetId="33"/>
-      <sheetData sheetId="34"/>
+      <sheetData sheetId="24" refreshError="1"/>
+      <sheetData sheetId="25" refreshError="1"/>
+      <sheetData sheetId="26" refreshError="1"/>
+      <sheetData sheetId="27" refreshError="1"/>
+      <sheetData sheetId="28" refreshError="1"/>
+      <sheetData sheetId="29" refreshError="1"/>
+      <sheetData sheetId="30" refreshError="1"/>
+      <sheetData sheetId="31" refreshError="1"/>
+      <sheetData sheetId="32" refreshError="1"/>
+      <sheetData sheetId="33" refreshError="1"/>
+      <sheetData sheetId="34" refreshError="1"/>
+      <sheetData sheetId="35" refreshError="1"/>
+      <sheetData sheetId="36" refreshError="1"/>
+      <sheetData sheetId="37" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -500,9 +506,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -535,26 +541,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -587,26 +576,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -781,19 +753,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1ED6F4FE-D4FD-4FAF-995E-613C0C8290EC}">
   <dimension ref="A1:K7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.6875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.5625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="4.140625" customWidth="1"/>
+    <col min="4" max="4" width="23.5625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="4.125" customWidth="1"/>
     <col min="8" max="8" width="6" customWidth="1"/>
     <col min="9" max="9" width="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -828,39 +800,39 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2">
         <v>5</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2">
         <v>10</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2">
         <v>200</v>
       </c>
-      <c r="E2" s="6">
+      <c r="E2" s="5">
         <f>B2-$B$6</f>
         <v>-5</v>
       </c>
-      <c r="F2" s="6">
+      <c r="F2" s="5">
         <f>-E2</f>
         <v>5</v>
       </c>
-      <c r="G2" s="6">
+      <c r="G2" s="5">
         <f>C2 - $C$6</f>
         <v>5</v>
       </c>
-      <c r="H2" s="6">
+      <c r="H2" s="5">
         <f>-G2</f>
         <v>-5</v>
       </c>
-      <c r="I2" s="5">
+      <c r="I2" s="4">
         <v>5</v>
       </c>
-      <c r="J2" s="5">
+      <c r="J2" s="4">
         <v>5</v>
       </c>
       <c r="K2">
@@ -868,39 +840,39 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3">
         <v>10</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3">
         <v>5</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3">
         <v>150</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="5">
         <f>B3-$B$6</f>
         <v>0</v>
       </c>
-      <c r="F3" s="6">
+      <c r="F3" s="5">
         <f t="shared" ref="F3:F5" si="0">-E3</f>
         <v>0</v>
       </c>
-      <c r="G3" s="6">
+      <c r="G3" s="5">
         <f>C3 - $C$6</f>
         <v>0</v>
       </c>
-      <c r="H3" s="6">
+      <c r="H3" s="5">
         <f t="shared" ref="H3:H5" si="1">-G3</f>
         <v>0</v>
       </c>
-      <c r="I3" s="5">
+      <c r="I3" s="4">
         <v>0</v>
       </c>
-      <c r="J3" s="5">
+      <c r="J3" s="4">
         <v>0</v>
       </c>
       <c r="K3">
@@ -908,39 +880,39 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4">
         <v>0</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4">
         <v>12</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4">
         <v>200</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="5">
         <f>B4-$B$6</f>
         <v>-10</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="5">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="5">
         <f>C4 - $C$6</f>
         <v>7</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="5">
         <f t="shared" si="1"/>
         <v>-7</v>
       </c>
-      <c r="I4" s="5">
+      <c r="I4" s="4">
         <v>10</v>
       </c>
-      <c r="J4" s="5">
+      <c r="J4" s="4">
         <v>7</v>
       </c>
       <c r="K4">
@@ -948,39 +920,39 @@
         <v>3400</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5">
         <v>12</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5">
         <v>0</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5">
         <v>300</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="5">
         <f>B5-$B$6</f>
         <v>2</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="5">
         <f t="shared" si="0"/>
         <v>-2</v>
       </c>
-      <c r="G5" s="6">
+      <c r="G5" s="5">
         <f>C5 - $C$6</f>
         <v>-5</v>
       </c>
-      <c r="H5" s="6">
+      <c r="H5" s="5">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="I5" s="5">
+      <c r="I5" s="4">
         <v>2</v>
       </c>
-      <c r="J5" s="5">
+      <c r="J5" s="4">
         <v>5</v>
       </c>
       <c r="K5">
@@ -988,26 +960,26 @@
         <v>2100</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="6">
         <v>10</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="6">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A7" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="4">
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="3">
         <f>SUM(K2:K5)</f>
         <v>7500</v>
       </c>
@@ -1024,7 +996,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D85756CD-BB6F-471C-AEDD-324919B9EA08}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
